--- a/docs/找号需求问卷.xlsx
+++ b/docs/找号需求问卷.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="144">
   <si>
     <t>问题</t>
   </si>
@@ -59,13 +59,13 @@
     <t>核心队伍(多选)</t>
   </si>
   <si>
-    <t>T0+和T0-队伍(完整榜单见Sheet2):庞统蜀步;豹纹刀;庞章鱼;变种王异刀;铁王八;三马队;九伐队;张飞流氓;大司机;程昱魏智;袁术网红;天马队;王异法刀;螃蟹队;大张鲁;变种钱步;龙虎骑;父子队;鬼无敌;同心队;飞天王八;纯刀;于禁蜀步;朱马刀;钱步;多马队;丑刀;三典藏菜刀;沙魏马</t>
+    <t>T0+/T0/T0-队伍(完整榜单见Sheet2):变种王异刀;庞统蜀步;三曹队;九伐队;鬼螭刀;三马队;胖章鱼;张飞流氓;黄盖神赏刀;曹彰物理骑;火烧鱼;司马霸府;变种黄盖刀;天马队;袁术王八;苟彧变种法刀;变种蜀步;袁术网红;飞天王八;豹纹刀;螃蟹队;属性刀;曹彰流氓;豹纹刀;黄盖法刀;变种桃步;于禁蜀步;朱马刀;程昱魏智;新晋核弹;袁术网红;天马队;王异法刀;螃蟹队;大张鲁;变种钱步;龙虎骑;父子队;鬼无敌;同心队;飞天王八;纯刀;于禁蜀步;朱马刀;钱步;多马队;丑刀;三典藏菜刀;沙魏马</t>
   </si>
   <si>
     <t>强度档要求</t>
   </si>
   <si>
-    <t>至少1支T0+;至少2支T0级;T1为主即可;越多越好</t>
+    <t>至少1支T0+;至少1支T0;至少2支T0级;T1为主即可;越多越好</t>
   </si>
   <si>
     <t>到手强度偏好</t>
@@ -122,6 +122,9 @@
     <t>T0+ (10支)</t>
   </si>
   <si>
+    <t>T0 (20支)</t>
+  </si>
+  <si>
     <t>T0- (19支)</t>
   </si>
   <si>
@@ -131,217 +134,256 @@
     <t>T2- (41支)</t>
   </si>
   <si>
+    <t>变种王异刀</t>
+  </si>
+  <si>
+    <t>火烧鱼</t>
+  </si>
+  <si>
+    <t>袁术网红</t>
+  </si>
+  <si>
+    <t>虎豹骑</t>
+  </si>
+  <si>
+    <t>打火机</t>
+  </si>
+  <si>
     <t>庞统蜀步</t>
   </si>
   <si>
-    <t>袁术网红</t>
-  </si>
-  <si>
-    <t>虎豹骑</t>
-  </si>
-  <si>
-    <t>打火机</t>
+    <t>司马霸府</t>
+  </si>
+  <si>
+    <t>天马队</t>
+  </si>
+  <si>
+    <t>聪明刀</t>
+  </si>
+  <si>
+    <t>狗刀</t>
+  </si>
+  <si>
+    <t>三曹队</t>
+  </si>
+  <si>
+    <t>变种黄盖刀</t>
+  </si>
+  <si>
+    <t>王异法刀</t>
+  </si>
+  <si>
+    <t>同心队</t>
+  </si>
+  <si>
+    <t>雨化田</t>
+  </si>
+  <si>
+    <t>九伐队</t>
+  </si>
+  <si>
+    <t>螃蟹队</t>
+  </si>
+  <si>
+    <t>大张鲁</t>
+  </si>
+  <si>
+    <t>新嘟嘟</t>
+  </si>
+  <si>
+    <t>鬼螭刀</t>
+  </si>
+  <si>
+    <t>袁术王八</t>
+  </si>
+  <si>
+    <t>定军赵</t>
+  </si>
+  <si>
+    <t>乐无敌</t>
+  </si>
+  <si>
+    <t>三马队</t>
+  </si>
+  <si>
+    <t>苟彧变种法刀</t>
+  </si>
+  <si>
+    <t>变种钱步</t>
+  </si>
+  <si>
+    <t>多弓队</t>
+  </si>
+  <si>
+    <t>衡轭菜刀</t>
+  </si>
+  <si>
+    <t>胖章鱼</t>
+  </si>
+  <si>
+    <t>变种蜀步</t>
+  </si>
+  <si>
+    <t>龙虎骑</t>
+  </si>
+  <si>
+    <t>关妹机关枪</t>
+  </si>
+  <si>
+    <t>核弹弓</t>
+  </si>
+  <si>
+    <t>张飞流氓</t>
+  </si>
+  <si>
+    <t>父子队</t>
+  </si>
+  <si>
+    <t>斩龙刀</t>
+  </si>
+  <si>
+    <t>胜兵嘟嘟</t>
+  </si>
+  <si>
+    <t>黄盖神赏刀</t>
+  </si>
+  <si>
+    <t>飞天王八</t>
+  </si>
+  <si>
+    <t>鬼无敌</t>
+  </si>
+  <si>
+    <t>马谡蜀骑</t>
+  </si>
+  <si>
+    <t>白嫖蜀刀</t>
+  </si>
+  <si>
+    <t>曹彰物理骑</t>
   </si>
   <si>
     <t>豹纹刀</t>
   </si>
   <si>
-    <t>天马队</t>
-  </si>
-  <si>
-    <t>聪明刀</t>
-  </si>
-  <si>
-    <t>狗刀</t>
-  </si>
-  <si>
-    <t>庞章鱼</t>
-  </si>
-  <si>
-    <t>王异法刀</t>
-  </si>
-  <si>
-    <t>同心队</t>
-  </si>
-  <si>
-    <t>雨化田</t>
-  </si>
-  <si>
-    <t>变种王异刀</t>
-  </si>
-  <si>
-    <t>螃蟹队</t>
-  </si>
-  <si>
-    <t>大张鲁</t>
-  </si>
-  <si>
-    <t>新嘟嘟</t>
-  </si>
-  <si>
-    <t>铁王八</t>
-  </si>
-  <si>
-    <t>定军歌</t>
-  </si>
-  <si>
-    <t>乐无敌</t>
-  </si>
-  <si>
-    <t>三马队</t>
-  </si>
-  <si>
-    <t>变种钱步</t>
+    <t>甘宁流氓</t>
+  </si>
+  <si>
+    <t>庞统肉队</t>
+  </si>
+  <si>
+    <t>周泰同心</t>
+  </si>
+  <si>
+    <t>赵维机</t>
+  </si>
+  <si>
+    <t>属性刀</t>
+  </si>
+  <si>
+    <t>纯刀</t>
+  </si>
+  <si>
+    <t>三贤队</t>
+  </si>
+  <si>
+    <t>传统魏智</t>
+  </si>
+  <si>
+    <t>曹彰流氓</t>
+  </si>
+  <si>
+    <t>于禁蜀步</t>
+  </si>
+  <si>
+    <t>合纵蜀骑</t>
+  </si>
+  <si>
+    <t>王异菜刀</t>
+  </si>
+  <si>
+    <t>朱马刀</t>
+  </si>
+  <si>
+    <t>三典藏菜刀</t>
+  </si>
+  <si>
+    <t>爷爷队</t>
+  </si>
+  <si>
+    <t>黄盖法刀</t>
+  </si>
+  <si>
+    <t>钱步</t>
+  </si>
+  <si>
+    <t>丁奉打火机</t>
+  </si>
+  <si>
+    <t>变种桃步</t>
   </si>
   <si>
     <t>多马队</t>
   </si>
   <si>
-    <t>衡轭菜刀</t>
-  </si>
-  <si>
-    <t>九伐队</t>
-  </si>
-  <si>
-    <t>龙虎骑</t>
-  </si>
-  <si>
-    <t>关妹机关枪</t>
-  </si>
-  <si>
-    <t>核弹弓</t>
-  </si>
-  <si>
-    <t>张飞流氓</t>
-  </si>
-  <si>
-    <t>父子队</t>
-  </si>
-  <si>
-    <t>斩龙刀</t>
-  </si>
-  <si>
-    <t>胜兵嘟嘟</t>
+    <t>孙形兵</t>
+  </si>
+  <si>
+    <t>丑刀</t>
+  </si>
+  <si>
+    <t>胡芳网红</t>
+  </si>
+  <si>
+    <t>变种物理刀</t>
+  </si>
+  <si>
+    <t>杜预菜刀</t>
+  </si>
+  <si>
+    <t>程昱魏智</t>
+  </si>
+  <si>
+    <t>沙魏马</t>
+  </si>
+  <si>
+    <t>马马曹</t>
+  </si>
+  <si>
+    <t>新晋核弹</t>
+  </si>
+  <si>
+    <t>变种虎豹骑</t>
+  </si>
+  <si>
+    <t>甘宁法刀</t>
+  </si>
+  <si>
+    <t>诸葛晋步</t>
+  </si>
+  <si>
+    <t>衡轭队</t>
+  </si>
+  <si>
+    <t>枭雄太刀</t>
+  </si>
+  <si>
+    <t>张绣撸铁队</t>
+  </si>
+  <si>
+    <t>曹彰法刀</t>
+  </si>
+  <si>
+    <t>法刀克星</t>
+  </si>
+  <si>
+    <t>豹形兵</t>
+  </si>
+  <si>
+    <t>温侯队</t>
   </si>
   <si>
     <t>大司机</t>
-  </si>
-  <si>
-    <t>鬼无敌</t>
-  </si>
-  <si>
-    <t>马腿蜀骑</t>
-  </si>
-  <si>
-    <t>白嫖蜀刀</t>
-  </si>
-  <si>
-    <t>程昱魏智</t>
-  </si>
-  <si>
-    <t>甘宁流氓</t>
-  </si>
-  <si>
-    <t>庞统肉队</t>
-  </si>
-  <si>
-    <t>飞天王八</t>
-  </si>
-  <si>
-    <t>周泰同心</t>
-  </si>
-  <si>
-    <t>赵维机</t>
-  </si>
-  <si>
-    <t>纯刀</t>
-  </si>
-  <si>
-    <t>三贤队</t>
-  </si>
-  <si>
-    <t>传统魏智</t>
-  </si>
-  <si>
-    <t>于禁蜀步</t>
-  </si>
-  <si>
-    <t>合纵蜀骑</t>
-  </si>
-  <si>
-    <t>王异菜刀</t>
-  </si>
-  <si>
-    <t>朱马刀</t>
-  </si>
-  <si>
-    <t>三典藏菜刀</t>
-  </si>
-  <si>
-    <t>爷爷队</t>
-  </si>
-  <si>
-    <t>钱步</t>
-  </si>
-  <si>
-    <t>丁奉打火机</t>
-  </si>
-  <si>
-    <t>孙张兵</t>
-  </si>
-  <si>
-    <t>丑刀</t>
-  </si>
-  <si>
-    <t>胡芳网红</t>
-  </si>
-  <si>
-    <t>变种物理刀</t>
-  </si>
-  <si>
-    <t>杜预菜刀</t>
-  </si>
-  <si>
-    <t>沙魏马</t>
-  </si>
-  <si>
-    <t>马马曹</t>
-  </si>
-  <si>
-    <t>变种虎豹骑</t>
-  </si>
-  <si>
-    <t>甘宁法刀</t>
-  </si>
-  <si>
-    <t>诸葛晋步</t>
-  </si>
-  <si>
-    <t>衡轭队</t>
-  </si>
-  <si>
-    <t>枭雄太刀</t>
-  </si>
-  <si>
-    <t>张绣撸铁队</t>
-  </si>
-  <si>
-    <t>曹彰法刀</t>
-  </si>
-  <si>
-    <t>法刀克星</t>
-  </si>
-  <si>
-    <t>豹形兵</t>
-  </si>
-  <si>
-    <t>温候队</t>
-  </si>
-  <si>
-    <t>大机己</t>
-  </si>
-  <si>
-    <t>属性刀</t>
   </si>
   <si>
     <t>正始大张张</t>
@@ -433,7 +475,7 @@
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -458,6 +500,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFED7D31"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -500,7 +547,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -517,6 +564,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1160,10 +1210,10 @@
       <formula1>"试师号,备战区,指定服务器,不限制"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C7">
-      <formula1>"庞统蜀步,豹纹刀,庞章鱼,变种王异刀,铁王八,三马队,九伐队,张飞流氓,大司机,程昱魏智,袁术网红,天马队,王异法刀,螃蟹队,大张鲁,变种钱步,龙虎骑,父子队,鬼无敌,同心队,飞天王八,纯刀,于禁蜀步,朱马刀,钱步,多马队,丑刀,三典藏菜刀,沙魏马"</formula1>
+      <formula1>"变种王异刀,庞统蜀步,三曹队,九伐队,鬼螭刀,三马队,胖章鱼,张飞流氓,黄盖神赏刀,曹彰物理骑,火烧鱼,司马霸府,变种黄盖刀,天马队,袁术王八,苟彧变种法刀,变种蜀步,袁术网红,飞天王八,豹纹刀,螃蟹队,属性刀,曹彰流氓,豹纹刀,黄盖法刀,变种桃步,于禁蜀步,朱马刀,程昱魏智,新晋核弹,袁术网红,天马队,王异法刀,螃蟹队,大张鲁,变种钱步,龙虎骑,父子队,鬼无敌,同心队,飞天王八,纯刀,于禁蜀步,朱马刀,钱步,多马队,丑刀,三典藏菜刀,沙魏马"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C8">
-      <formula1>"至少1支T0+,至少2支T0级,T1为主即可,越多越好"</formula1>
+      <formula1>"至少1支T0+,至少1支T0,至少2支T0级,T1为主即可,越多越好"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C9">
       <formula1>"武将全+战法宝可缺(推荐),到手即战力,只缺宝物,都要齐"</formula1>
@@ -1176,406 +1226,469 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="4" width="20" customWidth="1"/>
+    <col min="1" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D8" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
         <v>53</v>
       </c>
-      <c r="D5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="D11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>56</v>
-      </c>
-      <c r="D6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>66</v>
-      </c>
-      <c r="B9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" t="s">
-        <v>75</v>
-      </c>
-      <c r="D11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>77</v>
       </c>
       <c r="C12" t="s">
         <v>78</v>
       </c>
       <c r="D12" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="E16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
+        <v>106</v>
+      </c>
+      <c r="E18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D22" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D23" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="24" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D24" t="s">
+        <v>119</v>
+      </c>
+      <c r="E24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E26" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
-        <v>89</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
-      </c>
-      <c r="D16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>67</v>
-      </c>
-      <c r="D17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>92</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>87</v>
-      </c>
-      <c r="C19" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C22" t="s">
+    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
         <v>100</v>
       </c>
-      <c r="D22" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C23" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C24" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
+      <c r="E27" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D28" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C29" t="s">
-        <v>113</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="E28" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="29" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D29" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C30" t="s">
-        <v>115</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="E29" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D30" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C31" t="s">
-        <v>117</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="E30" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D31" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="32" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D32" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D38" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D39" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D40" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D41" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D42" t="s">
-        <v>129</v>
+        <v>131</v>
+      </c>
+      <c r="E31" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="32" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E32" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E40" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/docs/找号需求问卷.xlsx
+++ b/docs/找号需求问卷.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="144">
   <si>
     <t>问题</t>
   </si>
@@ -59,7 +59,7 @@
     <t>核心队伍(多选)</t>
   </si>
   <si>
-    <t>T0+/T0/T0-队伍(完整榜单见Sheet2):变种王异刀;庞统蜀步;三曹队;九伐队;鬼螭刀;三马队;胖章鱼;张飞流氓;黄盖神赏刀;曹彰物理骑;火烧鱼;司马霸府;变种黄盖刀;天马队;袁术王八;苟彧变种法刀;变种蜀步;袁术网红;飞天王八;豹纹刀;螃蟹队;属性刀;曹彰流氓;豹纹刀;黄盖法刀;变种桃步;于禁蜀步;朱马刀;程昱魏智;新晋核弹;袁术网红;天马队;王异法刀;螃蟹队;大张鲁;变种钱步;龙虎骑;父子队;鬼无敌;同心队;飞天王八;纯刀;于禁蜀步;朱马刀;钱步;多马队;丑刀;三典藏菜刀;沙魏马</t>
+    <t>T0+/T0队伍(完整榜单见Sheet2):变种王异刀;庞统蜀步;三曹队;九伐队;鬼螭刀;三马队;胖章鱼;张飞流氓;黄盖神赏刀;曹彰物理骑;火烧鱼;司马霸府;变种黄盖刀;天马队;袁术王八;苟彧变种法刀;变种蜀步;袁术网红;飞天王八;豹纹刀(曹彰);豹纹刀(曹纯);螃蟹队;属性刀;曹彰流氓;黄盖法刀;变种桃步;于禁蜀步;朱马刀;程昱魏智;新晋核弹</t>
   </si>
   <si>
     <t>强度档要求</t>
@@ -125,10 +125,7 @@
     <t>T0 (20支)</t>
   </si>
   <si>
-    <t>T0- (19支)</t>
-  </si>
-  <si>
-    <t>T1 (30支)</t>
+    <t>T1 (35支)</t>
   </si>
   <si>
     <t>T2- (41支)</t>
@@ -140,289 +137,292 @@
     <t>火烧鱼</t>
   </si>
   <si>
+    <t>虎豹骑</t>
+  </si>
+  <si>
+    <t>打火机</t>
+  </si>
+  <si>
+    <t>庞统蜀步</t>
+  </si>
+  <si>
+    <t>司马霸府</t>
+  </si>
+  <si>
+    <t>聪明刀</t>
+  </si>
+  <si>
+    <t>狗刀</t>
+  </si>
+  <si>
+    <t>三曹队</t>
+  </si>
+  <si>
+    <t>变种黄盖刀</t>
+  </si>
+  <si>
+    <t>同心队</t>
+  </si>
+  <si>
+    <t>雨化田</t>
+  </si>
+  <si>
+    <t>九伐队</t>
+  </si>
+  <si>
+    <t>天马队</t>
+  </si>
+  <si>
+    <t>大张鲁</t>
+  </si>
+  <si>
+    <t>新嘟嘟</t>
+  </si>
+  <si>
+    <t>鬼螭刀</t>
+  </si>
+  <si>
+    <t>袁术王八</t>
+  </si>
+  <si>
+    <t>定军赵</t>
+  </si>
+  <si>
+    <t>乐无敌</t>
+  </si>
+  <si>
+    <t>三马队</t>
+  </si>
+  <si>
+    <t>苟彧变种法刀</t>
+  </si>
+  <si>
+    <t>多弓队</t>
+  </si>
+  <si>
+    <t>衡轭菜刀</t>
+  </si>
+  <si>
+    <t>胖章鱼</t>
+  </si>
+  <si>
+    <t>变种蜀步</t>
+  </si>
+  <si>
+    <t>关妹机关枪</t>
+  </si>
+  <si>
+    <t>核弹弓</t>
+  </si>
+  <si>
+    <t>张飞流氓</t>
+  </si>
+  <si>
     <t>袁术网红</t>
   </si>
   <si>
-    <t>虎豹骑</t>
-  </si>
-  <si>
-    <t>打火机</t>
-  </si>
-  <si>
-    <t>庞统蜀步</t>
-  </si>
-  <si>
-    <t>司马霸府</t>
-  </si>
-  <si>
-    <t>天马队</t>
-  </si>
-  <si>
-    <t>聪明刀</t>
-  </si>
-  <si>
-    <t>狗刀</t>
-  </si>
-  <si>
-    <t>三曹队</t>
-  </si>
-  <si>
-    <t>变种黄盖刀</t>
+    <t>斩龙刀</t>
+  </si>
+  <si>
+    <t>胜兵嘟嘟</t>
+  </si>
+  <si>
+    <t>黄盖神赏刀</t>
+  </si>
+  <si>
+    <t>飞天王八</t>
+  </si>
+  <si>
+    <t>马谡蜀骑</t>
+  </si>
+  <si>
+    <t>白嫖蜀刀</t>
+  </si>
+  <si>
+    <t>曹彰物理骑</t>
+  </si>
+  <si>
+    <t>豹纹刀(曹彰)</t>
+  </si>
+  <si>
+    <t>甘宁流氓</t>
+  </si>
+  <si>
+    <t>庞统肉队</t>
+  </si>
+  <si>
+    <t>豹纹刀(曹纯)</t>
+  </si>
+  <si>
+    <t>周泰同心</t>
+  </si>
+  <si>
+    <t>赵维机</t>
+  </si>
+  <si>
+    <t>螃蟹队</t>
+  </si>
+  <si>
+    <t>三贤队</t>
+  </si>
+  <si>
+    <t>传统魏智</t>
+  </si>
+  <si>
+    <t>属性刀</t>
+  </si>
+  <si>
+    <t>合纵蜀骑</t>
+  </si>
+  <si>
+    <t>王异菜刀</t>
+  </si>
+  <si>
+    <t>曹彰流氓</t>
+  </si>
+  <si>
+    <t>三典藏菜刀</t>
+  </si>
+  <si>
+    <t>爷爷队</t>
+  </si>
+  <si>
+    <t>黄盖法刀</t>
+  </si>
+  <si>
+    <t>鬼无敌</t>
+  </si>
+  <si>
+    <t>丁奉打火机</t>
+  </si>
+  <si>
+    <t>变种桃步</t>
+  </si>
+  <si>
+    <t>父子队</t>
+  </si>
+  <si>
+    <t>孙形兵</t>
+  </si>
+  <si>
+    <t>于禁蜀步</t>
+  </si>
+  <si>
+    <t>胡芳网红</t>
+  </si>
+  <si>
+    <t>变种物理刀</t>
+  </si>
+  <si>
+    <t>朱马刀</t>
+  </si>
+  <si>
+    <t>龙虎骑</t>
+  </si>
+  <si>
+    <t>杜预菜刀</t>
+  </si>
+  <si>
+    <t>程昱魏智</t>
+  </si>
+  <si>
+    <t>纯刀</t>
+  </si>
+  <si>
+    <t>马马曹</t>
+  </si>
+  <si>
+    <t>新晋核弹</t>
+  </si>
+  <si>
+    <t>变种虎豹骑</t>
+  </si>
+  <si>
+    <t>甘宁法刀</t>
+  </si>
+  <si>
+    <t>诸葛晋步</t>
+  </si>
+  <si>
+    <t>衡轭队</t>
+  </si>
+  <si>
+    <t>枭雄太刀</t>
+  </si>
+  <si>
+    <t>张绣撸铁队</t>
+  </si>
+  <si>
+    <t>曹彰法刀</t>
+  </si>
+  <si>
+    <t>法刀克星</t>
+  </si>
+  <si>
+    <t>豹形兵</t>
+  </si>
+  <si>
+    <t>温侯队</t>
+  </si>
+  <si>
+    <t>大司机</t>
+  </si>
+  <si>
+    <t>钱步</t>
+  </si>
+  <si>
+    <t>正始大张张</t>
+  </si>
+  <si>
+    <t>五虎队</t>
+  </si>
+  <si>
+    <t>砍王</t>
+  </si>
+  <si>
+    <t>干锅队</t>
+  </si>
+  <si>
+    <t>皇无敌</t>
+  </si>
+  <si>
+    <t>弓吕网红</t>
+  </si>
+  <si>
+    <t>混元刀</t>
+  </si>
+  <si>
+    <t>神赏王八</t>
+  </si>
+  <si>
+    <t>蜀刀</t>
   </si>
   <si>
     <t>王异法刀</t>
   </si>
   <si>
-    <t>同心队</t>
-  </si>
-  <si>
-    <t>雨化田</t>
-  </si>
-  <si>
-    <t>九伐队</t>
-  </si>
-  <si>
-    <t>螃蟹队</t>
-  </si>
-  <si>
-    <t>大张鲁</t>
-  </si>
-  <si>
-    <t>新嘟嘟</t>
-  </si>
-  <si>
-    <t>鬼螭刀</t>
-  </si>
-  <si>
-    <t>袁术王八</t>
-  </si>
-  <si>
-    <t>定军赵</t>
-  </si>
-  <si>
-    <t>乐无敌</t>
-  </si>
-  <si>
-    <t>三马队</t>
-  </si>
-  <si>
-    <t>苟彧变种法刀</t>
+    <t>百战钢板</t>
   </si>
   <si>
     <t>变种钱步</t>
   </si>
   <si>
-    <t>多弓队</t>
-  </si>
-  <si>
-    <t>衡轭菜刀</t>
-  </si>
-  <si>
-    <t>胖章鱼</t>
-  </si>
-  <si>
-    <t>变种蜀步</t>
-  </si>
-  <si>
-    <t>龙虎骑</t>
-  </si>
-  <si>
-    <t>关妹机关枪</t>
-  </si>
-  <si>
-    <t>核弹弓</t>
-  </si>
-  <si>
-    <t>张飞流氓</t>
-  </si>
-  <si>
-    <t>父子队</t>
-  </si>
-  <si>
-    <t>斩龙刀</t>
-  </si>
-  <si>
-    <t>胜兵嘟嘟</t>
-  </si>
-  <si>
-    <t>黄盖神赏刀</t>
-  </si>
-  <si>
-    <t>飞天王八</t>
-  </si>
-  <si>
-    <t>鬼无敌</t>
-  </si>
-  <si>
-    <t>马谡蜀骑</t>
-  </si>
-  <si>
-    <t>白嫖蜀刀</t>
-  </si>
-  <si>
-    <t>曹彰物理骑</t>
-  </si>
-  <si>
-    <t>豹纹刀</t>
-  </si>
-  <si>
-    <t>甘宁流氓</t>
-  </si>
-  <si>
-    <t>庞统肉队</t>
-  </si>
-  <si>
-    <t>周泰同心</t>
-  </si>
-  <si>
-    <t>赵维机</t>
-  </si>
-  <si>
-    <t>属性刀</t>
-  </si>
-  <si>
-    <t>纯刀</t>
-  </si>
-  <si>
-    <t>三贤队</t>
-  </si>
-  <si>
-    <t>传统魏智</t>
-  </si>
-  <si>
-    <t>曹彰流氓</t>
-  </si>
-  <si>
-    <t>于禁蜀步</t>
-  </si>
-  <si>
-    <t>合纵蜀骑</t>
-  </si>
-  <si>
-    <t>王异菜刀</t>
-  </si>
-  <si>
-    <t>朱马刀</t>
-  </si>
-  <si>
-    <t>三典藏菜刀</t>
-  </si>
-  <si>
-    <t>爷爷队</t>
-  </si>
-  <si>
-    <t>黄盖法刀</t>
-  </si>
-  <si>
-    <t>钱步</t>
-  </si>
-  <si>
-    <t>丁奉打火机</t>
-  </si>
-  <si>
-    <t>变种桃步</t>
+    <t>徐庶蜀骑</t>
   </si>
   <si>
     <t>多马队</t>
   </si>
   <si>
-    <t>孙形兵</t>
+    <t>久战蜀智</t>
   </si>
   <si>
     <t>丑刀</t>
   </si>
   <si>
-    <t>胡芳网红</t>
-  </si>
-  <si>
-    <t>变种物理刀</t>
-  </si>
-  <si>
-    <t>杜预菜刀</t>
-  </si>
-  <si>
-    <t>程昱魏智</t>
+    <t>关羽砍王</t>
   </si>
   <si>
     <t>沙魏马</t>
-  </si>
-  <si>
-    <t>马马曹</t>
-  </si>
-  <si>
-    <t>新晋核弹</t>
-  </si>
-  <si>
-    <t>变种虎豹骑</t>
-  </si>
-  <si>
-    <t>甘宁法刀</t>
-  </si>
-  <si>
-    <t>诸葛晋步</t>
-  </si>
-  <si>
-    <t>衡轭队</t>
-  </si>
-  <si>
-    <t>枭雄太刀</t>
-  </si>
-  <si>
-    <t>张绣撸铁队</t>
-  </si>
-  <si>
-    <t>曹彰法刀</t>
-  </si>
-  <si>
-    <t>法刀克星</t>
-  </si>
-  <si>
-    <t>豹形兵</t>
-  </si>
-  <si>
-    <t>温侯队</t>
-  </si>
-  <si>
-    <t>大司机</t>
-  </si>
-  <si>
-    <t>正始大张张</t>
-  </si>
-  <si>
-    <t>五虎队</t>
-  </si>
-  <si>
-    <t>砍王</t>
-  </si>
-  <si>
-    <t>干锅队</t>
-  </si>
-  <si>
-    <t>皇无敌</t>
-  </si>
-  <si>
-    <t>弓吕网红</t>
-  </si>
-  <si>
-    <t>混元刀</t>
-  </si>
-  <si>
-    <t>神赏王八</t>
-  </si>
-  <si>
-    <t>蜀刀</t>
-  </si>
-  <si>
-    <t>百战钢板</t>
-  </si>
-  <si>
-    <t>徐庶蜀骑</t>
-  </si>
-  <si>
-    <t>久战蜀智</t>
-  </si>
-  <si>
-    <t>关羽砍王</t>
   </si>
   <si>
     <t>三皇</t>
@@ -475,7 +475,7 @@
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -500,11 +500,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFED7D31"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -547,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -564,9 +559,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1210,7 +1202,7 @@
       <formula1>"试师号,备战区,指定服务器,不限制"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C7">
-      <formula1>"变种王异刀,庞统蜀步,三曹队,九伐队,鬼螭刀,三马队,胖章鱼,张飞流氓,黄盖神赏刀,曹彰物理骑,火烧鱼,司马霸府,变种黄盖刀,天马队,袁术王八,苟彧变种法刀,变种蜀步,袁术网红,飞天王八,豹纹刀,螃蟹队,属性刀,曹彰流氓,豹纹刀,黄盖法刀,变种桃步,于禁蜀步,朱马刀,程昱魏智,新晋核弹,袁术网红,天马队,王异法刀,螃蟹队,大张鲁,变种钱步,龙虎骑,父子队,鬼无敌,同心队,飞天王八,纯刀,于禁蜀步,朱马刀,钱步,多马队,丑刀,三典藏菜刀,沙魏马"</formula1>
+      <formula1>"变种王异刀,庞统蜀步,三曹队,九伐队,鬼螭刀,三马队,胖章鱼,张飞流氓,黄盖神赏刀,曹彰物理骑,火烧鱼,司马霸府,变种黄盖刀,天马队,袁术王八,苟彧变种法刀,变种蜀步,袁术网红,飞天王八,豹纹刀(曹彰),豹纹刀(曹纯),螃蟹队,属性刀,曹彰流氓,黄盖法刀,变种桃步,于禁蜀步,朱马刀,程昱魏智,新晋核弹"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C8">
       <formula1>"至少1支T0+,至少1支T0,至少2支T0级,T1为主即可,越多越好"</formula1>
@@ -1226,468 +1218,423 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="5" width="20" customWidth="1"/>
+    <col min="1" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>41</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>42</v>
       </c>
-      <c r="D2" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>43</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C3" t="s">
         <v>45</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>46</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>47</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
         <v>48</v>
       </c>
-      <c r="E3" t="s">
+      <c r="C4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D4" t="s">
         <v>50</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>51</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" t="s">
         <v>52</v>
       </c>
-      <c r="D4" t="s">
+      <c r="C5" t="s">
         <v>53</v>
       </c>
-      <c r="E4" t="s">
+      <c r="D5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>55</v>
       </c>
-      <c r="B5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B6" t="s">
         <v>56</v>
-      </c>
-      <c r="D5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
       </c>
       <c r="C6" t="s">
         <v>57</v>
       </c>
       <c r="D6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" t="s">
         <v>61</v>
       </c>
-      <c r="E6" t="s">
+      <c r="D7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>63</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>64</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>65</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>66</v>
       </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
         <v>68</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C9" t="s">
         <v>69</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D9" t="s">
         <v>70</v>
       </c>
-      <c r="D8" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>71</v>
       </c>
-      <c r="E8" t="s">
+      <c r="B10" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="C10" t="s">
         <v>73</v>
       </c>
-      <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D10" t="s">
         <v>74</v>
       </c>
-      <c r="D9" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>75</v>
       </c>
-      <c r="E9" t="s">
+      <c r="B11" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="C11" t="s">
         <v>77</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D11" t="s">
         <v>78</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="D10" t="s">
+      <c r="C12" t="s">
         <v>80</v>
       </c>
-      <c r="E10" t="s">
+      <c r="D12" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
         <v>82</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C13" t="s">
         <v>83</v>
       </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="D13" t="s">
         <v>84</v>
       </c>
-      <c r="E11" t="s">
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C14" t="s">
         <v>86</v>
       </c>
-      <c r="E12" t="s">
+      <c r="D14" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
         <v>88</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C15" t="s">
         <v>89</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D15" t="s">
         <v>90</v>
       </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
+      <c r="C16" t="s">
         <v>92</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D16" t="s">
         <v>93</v>
       </c>
-      <c r="D14" t="s">
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>94</v>
       </c>
-      <c r="E14" t="s">
+      <c r="C17" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D17" t="s">
         <v>96</v>
       </c>
-      <c r="D15" t="s">
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>97</v>
       </c>
-      <c r="E15" t="s">
+      <c r="C18" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+      <c r="D18" t="s">
         <v>99</v>
       </c>
-      <c r="C16" t="s">
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
         <v>100</v>
       </c>
-      <c r="D16" t="s">
-        <v>79</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="C19" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
+      <c r="D19" t="s">
         <v>102</v>
       </c>
-      <c r="C17" t="s">
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
         <v>103</v>
       </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="C20" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D20" t="s">
         <v>105</v>
       </c>
-      <c r="D18" t="s">
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
         <v>106</v>
       </c>
-      <c r="E18" t="s">
+      <c r="C21" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>96</v>
-      </c>
-      <c r="C19" t="s">
-        <v>97</v>
-      </c>
-      <c r="D19" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" t="s">
+    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C22" t="s">
         <v>109</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D22" t="s">
         <v>110</v>
       </c>
-      <c r="D20" t="s">
-        <v>89</v>
-      </c>
-      <c r="E20" t="s">
+    </row>
+    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C23" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" t="s">
+      <c r="D23" t="s">
         <v>112</v>
       </c>
-      <c r="D21" t="s">
+    </row>
+    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C24" t="s">
         <v>113</v>
       </c>
-      <c r="E21" t="s">
+      <c r="D24" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D22" t="s">
+    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
         <v>115</v>
       </c>
-      <c r="E22" t="s">
+      <c r="D25" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D23" t="s">
+    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C26" t="s">
         <v>117</v>
       </c>
-      <c r="E23" t="s">
+      <c r="D26" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="24" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D24" t="s">
+      <c r="D27" t="s">
         <v>119</v>
       </c>
-      <c r="E24" t="s">
+    </row>
+    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="25" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D25" t="s">
+      <c r="D28" t="s">
         <v>121</v>
       </c>
-      <c r="E25" t="s">
+    </row>
+    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C29" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="26" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D26" t="s">
+      <c r="D29" t="s">
         <v>123</v>
       </c>
-      <c r="E26" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D27" t="s">
-        <v>100</v>
-      </c>
-      <c r="E27" t="s">
+    </row>
+    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C30" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="28" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D28" t="s">
+      <c r="D30" t="s">
         <v>125</v>
       </c>
-      <c r="E28" t="s">
+    </row>
+    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C31" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="29" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D29" t="s">
+      <c r="D31" t="s">
         <v>127</v>
       </c>
-      <c r="E29" t="s">
+    </row>
+    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C32" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="30" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D30" t="s">
+      <c r="D32" t="s">
         <v>129</v>
       </c>
-      <c r="E30" t="s">
+    </row>
+    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="31" spans="4:5" x14ac:dyDescent="0.25">
-      <c r="D31" t="s">
+      <c r="D33" t="s">
         <v>131</v>
       </c>
-      <c r="E31" t="s">
+    </row>
+    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C34" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="32" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E32" t="s">
+      <c r="D34" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E33" t="s">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C35" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E34" t="s">
+      <c r="D35" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E35" t="s">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C36" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="36" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E36" t="s">
+      <c r="D36" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E37" t="s">
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E38" t="s">
+    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E39" t="s">
+    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D39" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E40" t="s">
+    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D40" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E41" t="s">
+    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="5:5" x14ac:dyDescent="0.25">
-      <c r="E42" t="s">
+    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D42" t="s">
         <v>143</v>
       </c>
     </row>

--- a/docs/找号需求问卷.xlsx
+++ b/docs/找号需求问卷.xlsx
@@ -1,13 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\率土之滨\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowWidth="32745" windowHeight="17655"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="问卷" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="队伍强度榜" state="visible" r:id="rId5"/>
+    <sheet name="问卷" sheetId="1" r:id="rId1"/>
+    <sheet name="队伍强度榜" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -449,33 +470,216 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color rgb="FFC00000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FFC00000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -484,31 +688,222 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED7D31"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF808080"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED7D31"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF808080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -532,47 +927,360 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -894,278 +1602,278 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D19"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="1" max="1" width="26.1416666666667" customWidth="1"/>
+    <col min="2" max="2" width="50.625" customWidth="1"/>
+    <col min="3" max="3" width="24.975" customWidth="1"/>
+    <col min="4" max="4" width="8.80833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="3" customFormat="1" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" ht="39" customHeight="1" spans="1:4">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="C3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="C4" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="C5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="C6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" ht="88.5" customHeight="1" spans="1:4">
+      <c r="A7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="C7" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A8" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="C8" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="C9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="C10" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="B11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A12" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="B12" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A13" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+      <c r="B13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+      <c r="B14" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
+      <c r="C15" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A16" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+      <c r="C16" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A17" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+      <c r="C17" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A18" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="C18" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1" spans="1:4">
+      <c r="A19" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="B19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="10" t="s">
         <v>7</v>
       </c>
     </row>
@@ -1174,24 +1882,6 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C10">
-      <formula1>"宝物,战法,都可以,完全不补"</formula1>
-    </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="请输入数字" error="请输入大于等于0的整数" sqref="C11:C14">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C15">
-      <formula1>"不要求,核心武将2红以上,吃红度队伍要高红"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C16">
-      <formula1>"主力号,开荒号,小号,收藏体验"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C17">
-      <formula1>"立刻能打,1-2周内可补宝,不着急慢慢养"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C18">
-      <formula1>"3-5个候选加报告,单个最优加落地清单,协助下单"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C3">
       <formula1>"500以内,500-1000,1000-1500,1500-2000(推荐),2000-3000,3000以上"</formula1>
     </dataValidation>
@@ -1210,35 +1900,55 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C9">
       <formula1>"武将全+战法宝可缺(推荐),到手即战力,只缺宝物,都要齐"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C10">
+      <formula1>"宝物,战法,都可以,完全不补"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C15">
+      <formula1>"不要求,核心武将2红以上,吃红度队伍要高红"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C16">
+      <formula1>"主力号,开荒号,小号,收藏体验"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C17">
+      <formula1>"立刻能打,1-2周内可补宝,不着急慢慢养"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="请从列表选择" error="请点击单元格右侧下拉选择选项" sqref="C18">
+      <formula1>"3-5个候选加报告,单个最优加落地清单,协助下单"</formula1>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorTitle="请输入数字" error="请输入大于等于0的整数" sqref="C11:C14">
+      <formula1>0</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -1252,7 +1962,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -1266,7 +1976,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>47</v>
       </c>
@@ -1280,7 +1990,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -1294,7 +2004,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -1308,7 +2018,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -1322,7 +2032,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -1336,7 +2046,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -1350,7 +2060,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -1364,7 +2074,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -1378,7 +2088,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4">
       <c r="B12" t="s">
         <v>79</v>
       </c>
@@ -1389,7 +2099,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4">
       <c r="B13" t="s">
         <v>82</v>
       </c>
@@ -1400,7 +2110,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4">
       <c r="B14" t="s">
         <v>85</v>
       </c>
@@ -1411,7 +2121,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4">
       <c r="B15" t="s">
         <v>88</v>
       </c>
@@ -1422,7 +2132,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4">
       <c r="B16" t="s">
         <v>91</v>
       </c>
@@ -1433,7 +2143,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4">
       <c r="B17" t="s">
         <v>94</v>
       </c>
@@ -1444,7 +2154,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4">
       <c r="B18" t="s">
         <v>97</v>
       </c>
@@ -1455,7 +2165,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4">
       <c r="B19" t="s">
         <v>100</v>
       </c>
@@ -1466,7 +2176,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4">
       <c r="B20" t="s">
         <v>103</v>
       </c>
@@ -1477,7 +2187,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4">
       <c r="B21" t="s">
         <v>106</v>
       </c>
@@ -1488,7 +2198,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="22" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4">
       <c r="C22" t="s">
         <v>109</v>
       </c>
@@ -1496,7 +2206,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="23" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:4">
       <c r="C23" t="s">
         <v>111</v>
       </c>
@@ -1504,7 +2214,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="24" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:4">
       <c r="C24" t="s">
         <v>113</v>
       </c>
@@ -1512,7 +2222,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="25" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:4">
       <c r="C25" t="s">
         <v>115</v>
       </c>
@@ -1520,7 +2230,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="26" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:4">
       <c r="C26" t="s">
         <v>117</v>
       </c>
@@ -1528,7 +2238,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="27" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:4">
       <c r="C27" t="s">
         <v>118</v>
       </c>
@@ -1536,7 +2246,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:4">
       <c r="C28" t="s">
         <v>120</v>
       </c>
@@ -1544,7 +2254,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:4">
       <c r="C29" t="s">
         <v>122</v>
       </c>
@@ -1552,7 +2262,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="30" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:4">
       <c r="C30" t="s">
         <v>124</v>
       </c>
@@ -1560,7 +2270,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="31" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:4">
       <c r="C31" t="s">
         <v>126</v>
       </c>
@@ -1568,7 +2278,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="32" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:4">
       <c r="C32" t="s">
         <v>128</v>
       </c>
@@ -1576,7 +2286,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="33" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:4">
       <c r="C33" t="s">
         <v>130</v>
       </c>
@@ -1584,7 +2294,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="34" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:4">
       <c r="C34" t="s">
         <v>132</v>
       </c>
@@ -1592,7 +2302,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="35" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="3:4">
       <c r="C35" t="s">
         <v>134</v>
       </c>
@@ -1600,7 +2310,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:4">
       <c r="C36" t="s">
         <v>136</v>
       </c>
@@ -1608,38 +2318,39 @@
         <v>137</v>
       </c>
     </row>
-    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:4">
       <c r="D37" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:4">
       <c r="D38" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="39" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:4">
       <c r="D39" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:4">
       <c r="D40" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="41" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:4">
       <c r="D41" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="3:4">
       <c r="D42" t="s">
         <v>143</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>